--- a/output/selected.xlsx
+++ b/output/selected.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'筛选结果'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'筛选结果'!$A$1:$S$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,10 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -434,261 +433,214 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>代码</t>
+          <t>股票名称</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>股票板块</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>涨跌幅</t>
+          <t>主营业务</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>换手率</t>
+          <t>近1季度营收</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>量比</t>
+          <t>近1季度净利润</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>市盈率</t>
+          <t>近1季度净利润增速</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>总市值</t>
+          <t>近2季度营收</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>近2季度净利润</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>概念</t>
+          <t>近2季度净利润增速</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>命中结果</t>
+          <t>近3季度营收</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>近3季度净利润</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>近3季度净利润增速</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>近4季度营收</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>近4季度净利润</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>近4季度净利润增速</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>近X日涨幅</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>近A日涨幅</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>命中规则</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>筛选时间</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>000001</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>示例A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>示例A</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>软件服务</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>10亿</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0亿</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>9亿</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>计算机</t>
+          <t>0.9亿</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>人工智能;金融科技</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>8亿</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>技术面全部满足，且基本面/题材满足任一; 技术面; 涨幅在 0 到 7 个点之间; 换手率不低于 2%; 量比不低于 1; 基本面或题材; 市盈率 0 到 80; 市值不低于 50 亿; 概念包含人工智能</t>
+          <t>0.8亿</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-06-15 22:24:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>000002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>示例B</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8.1%</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>地产</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-06-15 22:24:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>600000</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>示例C</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>技术面全部满足，且基本面/题材满足任一; 技术面; 涨幅在 0 到 7 个点之间; 换手率不低于 2%; 量比不低于 1; 基本面或题材; 市值不低于 50 亿</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-06-15 22:24:54</t>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>7亿</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.7亿</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>近20日涨幅&gt;30.0%; 近5日涨幅&lt;=10.0%</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-06-15 23:08:58</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:S2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>